--- a/louvers/files/reference_xls/price_xls/beamc.xlsx
+++ b/louvers/files/reference_xls/price_xls/beamc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/files/reference_xls/price_xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/snigdhagoel/Documents/Vibrant Technik/vibrant-technik/offer-generator-test/louvers/files/reference_xls/price_xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{369AFD13-70F2-914C-9355-2F62AEC98984}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2A921D-032B-7347-AD92-829D0239D00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="28800" windowHeight="17660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -595,7 +595,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="6">
-        <v>5460</v>
+        <v>6006.0000000000009</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -611,7 +611,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="6">
-        <v>5990</v>
+        <v>6589.0000000000009</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
@@ -627,7 +627,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="6">
-        <v>6280</v>
+        <v>6908.0000000000009</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -643,7 +643,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="6">
-        <v>6600</v>
+        <v>7260.0000000000009</v>
       </c>
       <c r="C5" s="3"/>
       <c r="D5" s="4"/>
@@ -659,7 +659,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="6">
-        <v>6890</v>
+        <v>7579.0000000000009</v>
       </c>
       <c r="C6" s="3"/>
       <c r="D6" s="4"/>
@@ -675,7 +675,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="10">
-        <v>7190</v>
+        <v>7909.0000000000009</v>
       </c>
       <c r="C7" s="3"/>
     </row>
@@ -684,7 +684,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="10">
-        <v>7490</v>
+        <v>8239</v>
       </c>
       <c r="C8" s="3"/>
     </row>
@@ -693,7 +693,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="10">
-        <v>7790</v>
+        <v>8569</v>
       </c>
       <c r="C9" s="3"/>
     </row>
@@ -702,7 +702,7 @@
         <v>10</v>
       </c>
       <c r="B10" s="10">
-        <v>8100</v>
+        <v>8910</v>
       </c>
       <c r="C10" s="3"/>
     </row>
@@ -711,7 +711,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="10">
-        <v>8400</v>
+        <v>9240</v>
       </c>
       <c r="C11" s="3"/>
     </row>
@@ -720,7 +720,7 @@
         <v>12</v>
       </c>
       <c r="B12" s="10">
-        <v>8700</v>
+        <v>9570</v>
       </c>
       <c r="C12" s="3"/>
     </row>
